--- a/artfynd/A 5637-2026 artfynd.xlsx
+++ b/artfynd/A 5637-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328241</v>
       </c>
       <c r="B2" t="n">
-        <v>80254</v>
+        <v>80255</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131328245</v>
+        <v>131328244</v>
       </c>
       <c r="B6" t="n">
         <v>57884</v>
@@ -1174,7 +1174,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563161</v>
+        <v>563174</v>
       </c>
       <c r="R6" t="n">
-        <v>6927582</v>
+        <v>6927569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Sannolikt bohål i död gran. Hålet sitter en meter, eller knappt det, ovan mark och innerdiametern är omkring 4,5 cm.</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1261,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131328244</v>
+        <v>131328249</v>
       </c>
       <c r="B7" t="n">
         <v>57884</v>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563174</v>
+        <v>562998</v>
       </c>
       <c r="R7" t="n">
-        <v>6927569</v>
+        <v>6927552</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1381,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131328249</v>
+        <v>131328245</v>
       </c>
       <c r="B8" t="n">
         <v>57884</v>
@@ -1414,7 +1414,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562998</v>
+        <v>563161</v>
       </c>
       <c r="R8" t="n">
-        <v>6927552</v>
+        <v>6927582</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>Sannolikt bohål i död gran. Hålet sitter en meter, eller knappt det, ovan mark och innerdiametern är omkring 4,5 cm.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131328237</v>
+        <v>131328251</v>
       </c>
       <c r="B9" t="n">
-        <v>91813</v>
+        <v>57884</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,34 +1512,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stockbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563065</v>
+        <v>563042</v>
       </c>
       <c r="R9" t="n">
-        <v>6927731</v>
+        <v>6927662</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,7 +1589,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131328251</v>
+        <v>131328237</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>91814</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,42 +1632,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stockbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563042</v>
+        <v>563065</v>
       </c>
       <c r="R10" t="n">
-        <v>6927662</v>
+        <v>6927731</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,12 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1848,32 +1848,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131328240</v>
+        <v>131328246</v>
       </c>
       <c r="B12" t="n">
-        <v>80254</v>
+        <v>91814</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563078</v>
+        <v>563144</v>
       </c>
       <c r="R12" t="n">
-        <v>6927684</v>
+        <v>6927589</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,32 +1955,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131328246</v>
+        <v>131328240</v>
       </c>
       <c r="B13" t="n">
-        <v>91813</v>
+        <v>80255</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563144</v>
+        <v>563078</v>
       </c>
       <c r="R13" t="n">
-        <v>6927589</v>
+        <v>6927684</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,7 +2065,7 @@
         <v>131328236</v>
       </c>
       <c r="B14" t="n">
-        <v>92111</v>
+        <v>92112</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>131328243</v>
       </c>
       <c r="B16" t="n">
-        <v>80350</v>
+        <v>80351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 5637-2026 artfynd.xlsx
+++ b/artfynd/A 5637-2026 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131328250</v>
+        <v>131328247</v>
       </c>
       <c r="B3" t="n">
-        <v>58043</v>
+        <v>57884</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,33 +793,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -829,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563040</v>
+        <v>563043</v>
       </c>
       <c r="R3" t="n">
-        <v>6927651</v>
+        <v>6927531</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328247</v>
+        <v>131328250</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>58043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,29 +913,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563043</v>
+        <v>563040</v>
       </c>
       <c r="R4" t="n">
-        <v>6927531</v>
+        <v>6927651</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 5637-2026 artfynd.xlsx
+++ b/artfynd/A 5637-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328241</v>
       </c>
       <c r="B2" t="n">
-        <v>80255</v>
+        <v>80257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131328247</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131328250</v>
       </c>
       <c r="B4" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>131328239</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>131328244</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>131328249</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>131328245</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>131328251</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>131328237</v>
       </c>
       <c r="B10" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>131328242</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131328246</v>
+        <v>131328240</v>
       </c>
       <c r="B12" t="n">
-        <v>91814</v>
+        <v>80257</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563144</v>
+        <v>563078</v>
       </c>
       <c r="R12" t="n">
-        <v>6927589</v>
+        <v>6927684</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,32 +1955,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131328240</v>
+        <v>131328246</v>
       </c>
       <c r="B13" t="n">
-        <v>80255</v>
+        <v>91816</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563078</v>
+        <v>563144</v>
       </c>
       <c r="R13" t="n">
-        <v>6927684</v>
+        <v>6927589</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,7 +2065,7 @@
         <v>131328236</v>
       </c>
       <c r="B14" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>131328248</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>131328243</v>
       </c>
       <c r="B16" t="n">
-        <v>80351</v>
+        <v>80353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 5637-2026 artfynd.xlsx
+++ b/artfynd/A 5637-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328241</v>
       </c>
       <c r="B2" t="n">
-        <v>80257</v>
+        <v>80258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131328247</v>
+        <v>131328250</v>
       </c>
       <c r="B3" t="n">
-        <v>57886</v>
+        <v>58046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,29 +793,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -825,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563043</v>
+        <v>563040</v>
       </c>
       <c r="R3" t="n">
-        <v>6927531</v>
+        <v>6927651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328250</v>
+        <v>131328247</v>
       </c>
       <c r="B4" t="n">
-        <v>58045</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,33 +912,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563040</v>
+        <v>563043</v>
       </c>
       <c r="R4" t="n">
-        <v>6927651</v>
+        <v>6927531</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
         <v>131328239</v>
       </c>
       <c r="B5" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>131328244</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>131328249</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>131328245</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131328251</v>
+        <v>131328237</v>
       </c>
       <c r="B9" t="n">
-        <v>57886</v>
+        <v>91817</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,42 +1512,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stockbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563042</v>
+        <v>563065</v>
       </c>
       <c r="R9" t="n">
-        <v>6927662</v>
+        <v>6927731</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,7 +1571,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,12 +1581,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131328237</v>
+        <v>131328251</v>
       </c>
       <c r="B10" t="n">
-        <v>91816</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,34 +1619,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stockbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563065</v>
+        <v>563042</v>
       </c>
       <c r="R10" t="n">
-        <v>6927731</v>
+        <v>6927662</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1696,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,7 +1731,7 @@
         <v>131328242</v>
       </c>
       <c r="B11" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131328240</v>
+        <v>131328246</v>
       </c>
       <c r="B12" t="n">
-        <v>80257</v>
+        <v>91817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563078</v>
+        <v>563144</v>
       </c>
       <c r="R12" t="n">
-        <v>6927684</v>
+        <v>6927589</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,32 +1955,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131328246</v>
+        <v>131328240</v>
       </c>
       <c r="B13" t="n">
-        <v>91816</v>
+        <v>80258</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563144</v>
+        <v>563078</v>
       </c>
       <c r="R13" t="n">
-        <v>6927589</v>
+        <v>6927684</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2065,7 +2065,7 @@
         <v>131328236</v>
       </c>
       <c r="B14" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>131328248</v>
       </c>
       <c r="B15" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>131328243</v>
       </c>
       <c r="B16" t="n">
-        <v>80353</v>
+        <v>80354</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 5637-2026 artfynd.xlsx
+++ b/artfynd/A 5637-2026 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131328250</v>
+        <v>131328247</v>
       </c>
       <c r="B3" t="n">
-        <v>58046</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,33 +793,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -829,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563040</v>
+        <v>563043</v>
       </c>
       <c r="R3" t="n">
-        <v>6927651</v>
+        <v>6927531</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328247</v>
+        <v>131328250</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>58046</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,29 +913,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563043</v>
+        <v>563040</v>
       </c>
       <c r="R4" t="n">
-        <v>6927531</v>
+        <v>6927651</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1848,32 +1848,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131328246</v>
+        <v>131328240</v>
       </c>
       <c r="B12" t="n">
-        <v>91817</v>
+        <v>80258</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563144</v>
+        <v>563078</v>
       </c>
       <c r="R12" t="n">
-        <v>6927589</v>
+        <v>6927684</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,32 +1955,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131328240</v>
+        <v>131328246</v>
       </c>
       <c r="B13" t="n">
-        <v>80258</v>
+        <v>91817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563078</v>
+        <v>563144</v>
       </c>
       <c r="R13" t="n">
-        <v>6927684</v>
+        <v>6927589</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 5637-2026 artfynd.xlsx
+++ b/artfynd/A 5637-2026 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131328247</v>
+        <v>131328250</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>58046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,29 +793,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -825,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563043</v>
+        <v>563040</v>
       </c>
       <c r="R3" t="n">
-        <v>6927531</v>
+        <v>6927651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328250</v>
+        <v>131328247</v>
       </c>
       <c r="B4" t="n">
-        <v>58046</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,33 +912,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563040</v>
+        <v>563043</v>
       </c>
       <c r="R4" t="n">
-        <v>6927651</v>
+        <v>6927531</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131328237</v>
+        <v>131328251</v>
       </c>
       <c r="B9" t="n">
-        <v>91817</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,34 +1512,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stockbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563065</v>
+        <v>563042</v>
       </c>
       <c r="R9" t="n">
-        <v>6927731</v>
+        <v>6927662</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,7 +1589,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131328251</v>
+        <v>131328237</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>91817</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,42 +1632,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stockbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563042</v>
+        <v>563065</v>
       </c>
       <c r="R10" t="n">
-        <v>6927662</v>
+        <v>6927731</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,12 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1848,32 +1848,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131328240</v>
+        <v>131328246</v>
       </c>
       <c r="B12" t="n">
-        <v>80258</v>
+        <v>91817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563078</v>
+        <v>563144</v>
       </c>
       <c r="R12" t="n">
-        <v>6927684</v>
+        <v>6927589</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,32 +1955,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131328246</v>
+        <v>131328240</v>
       </c>
       <c r="B13" t="n">
-        <v>91817</v>
+        <v>80258</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563144</v>
+        <v>563078</v>
       </c>
       <c r="R13" t="n">
-        <v>6927589</v>
+        <v>6927684</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 5637-2026 artfynd.xlsx
+++ b/artfynd/A 5637-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328241</v>
       </c>
       <c r="B2" t="n">
-        <v>80263</v>
+        <v>80269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131328247</v>
       </c>
       <c r="B3" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131328250</v>
       </c>
       <c r="B4" t="n">
-        <v>58051</v>
+        <v>58057</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>131328239</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>131328244</v>
       </c>
       <c r="B6" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>131328249</v>
       </c>
       <c r="B7" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>131328245</v>
       </c>
       <c r="B8" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131328237</v>
+        <v>131328251</v>
       </c>
       <c r="B9" t="n">
-        <v>91822</v>
+        <v>57898</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,34 +1512,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stockbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563065</v>
+        <v>563042</v>
       </c>
       <c r="R9" t="n">
-        <v>6927731</v>
+        <v>6927662</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,7 +1589,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131328251</v>
+        <v>131328237</v>
       </c>
       <c r="B10" t="n">
-        <v>57892</v>
+        <v>91828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,42 +1632,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stockbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563042</v>
+        <v>563065</v>
       </c>
       <c r="R10" t="n">
-        <v>6927662</v>
+        <v>6927731</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,12 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,7 +1731,7 @@
         <v>131328242</v>
       </c>
       <c r="B11" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>131328246</v>
       </c>
       <c r="B12" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131328240</v>
       </c>
       <c r="B13" t="n">
-        <v>80263</v>
+        <v>80269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>131328236</v>
       </c>
       <c r="B14" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>131328248</v>
       </c>
       <c r="B15" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>131328243</v>
       </c>
       <c r="B16" t="n">
-        <v>80359</v>
+        <v>80365</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 5637-2026 artfynd.xlsx
+++ b/artfynd/A 5637-2026 artfynd.xlsx
@@ -1501,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131328251</v>
+        <v>131328237</v>
       </c>
       <c r="B9" t="n">
-        <v>57898</v>
+        <v>91828</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,42 +1512,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stockbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563042</v>
+        <v>563065</v>
       </c>
       <c r="R9" t="n">
-        <v>6927662</v>
+        <v>6927731</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,7 +1571,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,12 +1581,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131328237</v>
+        <v>131328251</v>
       </c>
       <c r="B10" t="n">
-        <v>91828</v>
+        <v>57898</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,34 +1619,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stockbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563065</v>
+        <v>563042</v>
       </c>
       <c r="R10" t="n">
-        <v>6927731</v>
+        <v>6927662</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1696,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 5637-2026 artfynd.xlsx
+++ b/artfynd/A 5637-2026 artfynd.xlsx
@@ -1141,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131328244</v>
+        <v>131328245</v>
       </c>
       <c r="B6" t="n">
         <v>57898</v>
@@ -1174,7 +1174,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563174</v>
+        <v>563161</v>
       </c>
       <c r="R6" t="n">
-        <v>6927569</v>
+        <v>6927582</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>Sannolikt bohål i död gran. Hålet sitter en meter, eller knappt det, ovan mark och innerdiametern är omkring 4,5 cm.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1261,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131328249</v>
+        <v>131328244</v>
       </c>
       <c r="B7" t="n">
         <v>57898</v>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562998</v>
+        <v>563174</v>
       </c>
       <c r="R7" t="n">
-        <v>6927552</v>
+        <v>6927569</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1381,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131328245</v>
+        <v>131328249</v>
       </c>
       <c r="B8" t="n">
         <v>57898</v>
@@ -1414,7 +1414,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563161</v>
+        <v>562998</v>
       </c>
       <c r="R8" t="n">
-        <v>6927582</v>
+        <v>6927552</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Sannolikt bohål i död gran. Hålet sitter en meter, eller knappt det, ovan mark och innerdiametern är omkring 4,5 cm.</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1848,32 +1848,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131328246</v>
+        <v>131328240</v>
       </c>
       <c r="B12" t="n">
-        <v>91828</v>
+        <v>80269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563144</v>
+        <v>563078</v>
       </c>
       <c r="R12" t="n">
-        <v>6927589</v>
+        <v>6927684</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,32 +1955,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131328240</v>
+        <v>131328246</v>
       </c>
       <c r="B13" t="n">
-        <v>80269</v>
+        <v>91828</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563078</v>
+        <v>563144</v>
       </c>
       <c r="R13" t="n">
-        <v>6927684</v>
+        <v>6927589</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 5637-2026 artfynd.xlsx
+++ b/artfynd/A 5637-2026 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131328247</v>
+        <v>131328250</v>
       </c>
       <c r="B3" t="n">
-        <v>57898</v>
+        <v>58057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,29 +793,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -825,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563043</v>
+        <v>563040</v>
       </c>
       <c r="R3" t="n">
-        <v>6927531</v>
+        <v>6927651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328250</v>
+        <v>131328247</v>
       </c>
       <c r="B4" t="n">
-        <v>58057</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,33 +912,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563040</v>
+        <v>563043</v>
       </c>
       <c r="R4" t="n">
-        <v>6927651</v>
+        <v>6927531</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1141,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131328245</v>
+        <v>131328244</v>
       </c>
       <c r="B6" t="n">
         <v>57898</v>
@@ -1174,7 +1174,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563161</v>
+        <v>563174</v>
       </c>
       <c r="R6" t="n">
-        <v>6927582</v>
+        <v>6927569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Sannolikt bohål i död gran. Hålet sitter en meter, eller knappt det, ovan mark och innerdiametern är omkring 4,5 cm.</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,7 +1261,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131328244</v>
+        <v>131328249</v>
       </c>
       <c r="B7" t="n">
         <v>57898</v>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563174</v>
+        <v>562998</v>
       </c>
       <c r="R7" t="n">
-        <v>6927569</v>
+        <v>6927552</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1381,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131328249</v>
+        <v>131328245</v>
       </c>
       <c r="B8" t="n">
         <v>57898</v>
@@ -1414,7 +1414,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>562998</v>
+        <v>563161</v>
       </c>
       <c r="R8" t="n">
-        <v>6927552</v>
+        <v>6927582</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>Sannolikt bohål i död gran. Hålet sitter en meter, eller knappt det, ovan mark och innerdiametern är omkring 4,5 cm.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2065,7 +2065,7 @@
         <v>131328236</v>
       </c>
       <c r="B14" t="n">
-        <v>92126</v>
+        <v>92127</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 5637-2026 artfynd.xlsx
+++ b/artfynd/A 5637-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328241</v>
       </c>
       <c r="B2" t="n">
-        <v>80269</v>
+        <v>80270</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131328250</v>
       </c>
       <c r="B3" t="n">
-        <v>58057</v>
+        <v>58058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>131328247</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         <v>131328239</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>131328244</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>131328249</v>
       </c>
       <c r="B7" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>131328245</v>
       </c>
       <c r="B8" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>131328237</v>
       </c>
       <c r="B9" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>131328251</v>
       </c>
       <c r="B10" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>131328242</v>
       </c>
       <c r="B11" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>131328240</v>
       </c>
       <c r="B12" t="n">
-        <v>80269</v>
+        <v>80270</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131328246</v>
       </c>
       <c r="B13" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>131328236</v>
       </c>
       <c r="B14" t="n">
-        <v>92127</v>
+        <v>92128</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>131328248</v>
       </c>
       <c r="B15" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>131328243</v>
       </c>
       <c r="B16" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 5637-2026 artfynd.xlsx
+++ b/artfynd/A 5637-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328241</v>
       </c>
       <c r="B2" t="n">
-        <v>80270</v>
+        <v>80273</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131328250</v>
+        <v>131328247</v>
       </c>
       <c r="B3" t="n">
-        <v>58058</v>
+        <v>57902</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,33 +793,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -829,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563040</v>
+        <v>563043</v>
       </c>
       <c r="R3" t="n">
-        <v>6927651</v>
+        <v>6927531</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328247</v>
+        <v>131328250</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>58061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,29 +913,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563043</v>
+        <v>563040</v>
       </c>
       <c r="R4" t="n">
-        <v>6927531</v>
+        <v>6927651</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,12 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
         <v>131328239</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>131328244</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1264,7 +1264,7 @@
         <v>131328249</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>131328245</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131328237</v>
+        <v>131328251</v>
       </c>
       <c r="B9" t="n">
-        <v>91829</v>
+        <v>57902</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,34 +1512,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stockbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563065</v>
+        <v>563042</v>
       </c>
       <c r="R9" t="n">
-        <v>6927731</v>
+        <v>6927662</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,7 +1589,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131328251</v>
+        <v>131328237</v>
       </c>
       <c r="B10" t="n">
-        <v>57899</v>
+        <v>91832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,42 +1632,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stockbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563042</v>
+        <v>563065</v>
       </c>
       <c r="R10" t="n">
-        <v>6927662</v>
+        <v>6927731</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,12 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,7 +1731,7 @@
         <v>131328242</v>
       </c>
       <c r="B11" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>131328240</v>
       </c>
       <c r="B12" t="n">
-        <v>80270</v>
+        <v>80273</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131328246</v>
       </c>
       <c r="B13" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>131328236</v>
       </c>
       <c r="B14" t="n">
-        <v>92128</v>
+        <v>92131</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>131328248</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>131328243</v>
       </c>
       <c r="B16" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 5637-2026 artfynd.xlsx
+++ b/artfynd/A 5637-2026 artfynd.xlsx
@@ -1141,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131328244</v>
+        <v>131328245</v>
       </c>
       <c r="B6" t="n">
         <v>57902</v>
@@ -1174,7 +1174,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563174</v>
+        <v>563161</v>
       </c>
       <c r="R6" t="n">
-        <v>6927569</v>
+        <v>6927582</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>Sannolikt bohål i död gran. Hålet sitter en meter, eller knappt det, ovan mark och innerdiametern är omkring 4,5 cm.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1381,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131328245</v>
+        <v>131328244</v>
       </c>
       <c r="B8" t="n">
         <v>57902</v>
@@ -1414,7 +1414,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563161</v>
+        <v>563174</v>
       </c>
       <c r="R8" t="n">
-        <v>6927582</v>
+        <v>6927569</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Sannolikt bohål i död gran. Hålet sitter en meter, eller knappt det, ovan mark och innerdiametern är omkring 4,5 cm.</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131328251</v>
+        <v>131328237</v>
       </c>
       <c r="B9" t="n">
-        <v>57902</v>
+        <v>91832</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,42 +1512,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stockbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563042</v>
+        <v>563065</v>
       </c>
       <c r="R9" t="n">
-        <v>6927662</v>
+        <v>6927731</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,7 +1571,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,12 +1581,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,10 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131328237</v>
+        <v>131328251</v>
       </c>
       <c r="B10" t="n">
-        <v>91832</v>
+        <v>57902</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1632,34 +1619,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stockbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563065</v>
+        <v>563042</v>
       </c>
       <c r="R10" t="n">
-        <v>6927731</v>
+        <v>6927662</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1701,7 +1696,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1848,32 +1848,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131328240</v>
+        <v>131328246</v>
       </c>
       <c r="B12" t="n">
-        <v>80273</v>
+        <v>91832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563078</v>
+        <v>563144</v>
       </c>
       <c r="R12" t="n">
-        <v>6927684</v>
+        <v>6927589</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,32 +1955,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131328246</v>
+        <v>131328240</v>
       </c>
       <c r="B13" t="n">
-        <v>91832</v>
+        <v>80273</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563144</v>
+        <v>563078</v>
       </c>
       <c r="R13" t="n">
-        <v>6927589</v>
+        <v>6927684</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 5637-2026 artfynd.xlsx
+++ b/artfynd/A 5637-2026 artfynd.xlsx
@@ -1141,7 +1141,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131328245</v>
+        <v>131328244</v>
       </c>
       <c r="B6" t="n">
         <v>57902</v>
@@ -1174,7 +1174,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563161</v>
+        <v>563174</v>
       </c>
       <c r="R6" t="n">
-        <v>6927582</v>
+        <v>6927569</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Sannolikt bohål i död gran. Hålet sitter en meter, eller knappt det, ovan mark och innerdiametern är omkring 4,5 cm.</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1381,7 +1381,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131328244</v>
+        <v>131328245</v>
       </c>
       <c r="B8" t="n">
         <v>57902</v>
@@ -1414,7 +1414,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1424,10 +1424,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563174</v>
+        <v>563161</v>
       </c>
       <c r="R8" t="n">
-        <v>6927569</v>
+        <v>6927582</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1459,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>Sannolikt bohål i död gran. Hålet sitter en meter, eller knappt det, ovan mark och innerdiametern är omkring 4,5 cm.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1848,32 +1848,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131328246</v>
+        <v>131328240</v>
       </c>
       <c r="B12" t="n">
-        <v>91832</v>
+        <v>80273</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>563144</v>
+        <v>563078</v>
       </c>
       <c r="R12" t="n">
-        <v>6927589</v>
+        <v>6927684</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,32 +1955,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131328240</v>
+        <v>131328246</v>
       </c>
       <c r="B13" t="n">
-        <v>80273</v>
+        <v>91832</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1990,10 +1990,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>563078</v>
+        <v>563144</v>
       </c>
       <c r="R13" t="n">
-        <v>6927684</v>
+        <v>6927589</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2025,7 +2025,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 5637-2026 artfynd.xlsx
+++ b/artfynd/A 5637-2026 artfynd.xlsx
@@ -1501,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131328237</v>
+        <v>131328251</v>
       </c>
       <c r="B9" t="n">
-        <v>91832</v>
+        <v>57902</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,34 +1512,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stockbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563065</v>
+        <v>563042</v>
       </c>
       <c r="R9" t="n">
-        <v>6927731</v>
+        <v>6927662</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1579,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,7 +1589,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1608,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131328251</v>
+        <v>131328237</v>
       </c>
       <c r="B10" t="n">
-        <v>57902</v>
+        <v>91832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,42 +1632,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stockbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>563042</v>
+        <v>563065</v>
       </c>
       <c r="R10" t="n">
-        <v>6927662</v>
+        <v>6927731</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1691,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,12 +1701,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:53</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 5637-2026 artfynd.xlsx
+++ b/artfynd/A 5637-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131328241</v>
       </c>
       <c r="B2" t="n">
-        <v>80273</v>
+        <v>80275</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131328247</v>
+        <v>131328250</v>
       </c>
       <c r="B3" t="n">
-        <v>57902</v>
+        <v>58063</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,29 +793,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -825,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563043</v>
+        <v>563040</v>
       </c>
       <c r="R3" t="n">
-        <v>6927531</v>
+        <v>6927651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131328250</v>
+        <v>131328247</v>
       </c>
       <c r="B4" t="n">
-        <v>58061</v>
+        <v>57904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,33 +912,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563040</v>
+        <v>563043</v>
       </c>
       <c r="R4" t="n">
-        <v>6927651</v>
+        <v>6927531</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,7 +1024,7 @@
         <v>131328239</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131328244</v>
+        <v>131328249</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563174</v>
+        <v>562998</v>
       </c>
       <c r="R6" t="n">
-        <v>6927569</v>
+        <v>6927552</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:44</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131328249</v>
+        <v>131328244</v>
       </c>
       <c r="B7" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>562998</v>
+        <v>563174</v>
       </c>
       <c r="R7" t="n">
-        <v>6927552</v>
+        <v>6927569</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1384,7 +1384,7 @@
         <v>131328245</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
         <v>131328251</v>
       </c>
       <c r="B9" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>131328237</v>
       </c>
       <c r="B10" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
         <v>131328242</v>
       </c>
       <c r="B11" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>131328240</v>
       </c>
       <c r="B12" t="n">
-        <v>80273</v>
+        <v>80275</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>131328246</v>
       </c>
       <c r="B13" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         <v>131328236</v>
       </c>
       <c r="B14" t="n">
-        <v>92131</v>
+        <v>92137</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>131328248</v>
       </c>
       <c r="B15" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>131328243</v>
       </c>
       <c r="B16" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
